--- a/docs/test-cases/SPM-65_Test_Cases.xlsx
+++ b/docs/test-cases/SPM-65_Test_Cases.xlsx
@@ -19,11 +19,6 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TC10" sheetId="11" state="visible" r:id="rId11"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TC11" sheetId="12" state="visible" r:id="rId12"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TC12" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TC13" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TC14" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TC15" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TC16" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TC17" sheetId="18" state="visible" r:id="rId18"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -463,7 +458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F34"/>
+  <dimension ref="A1:F29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -535,12 +530,12 @@
       </c>
       <c r="C4" s="11" t="inlineStr">
         <is>
-          <t>The organiser responsible for the event opens its Attendees tab and sees each attendee's name, email and registration date</t>
+          <t>The organiser responsible for a full event sees every attendee with their contact details, status and registration date, who was added on their behalf, and the places taken against the waiting list</t>
         </is>
       </c>
       <c r="D4" s="11" t="inlineStr">
         <is>
-          <t>AC1, AC2</t>
+          <t>AC1, AC2, AC3, AC4, AC5</t>
         </is>
       </c>
       <c r="E4" s="11" t="inlineStr">
@@ -567,12 +562,12 @@
       </c>
       <c r="C5" s="11" t="inlineStr">
         <is>
-          <t>Registered, waitlisted and withdrawn attendees each have their own status badge, and a withdrawn one shows when they withdrew</t>
+          <t>Checked-in attendees of a past event are shown as Attended, apart from those who registered but did not come and those who withdrew</t>
         </is>
       </c>
       <c r="D5" s="11" t="inlineStr">
         <is>
-          <t>AC3</t>
+          <t>AC3, AC5</t>
         </is>
       </c>
       <c r="E5" s="11" t="inlineStr">
@@ -599,22 +594,22 @@
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>An attendee added on the organiser's behalf is marked with who added them, and self-registered attendees are not</t>
+          <t>An event with no capacity limit shows how many are registered and says there is no limit</t>
         </is>
       </c>
       <c r="D6" s="11" t="inlineStr">
         <is>
-          <t>AC4</t>
+          <t>AC5</t>
         </is>
       </c>
       <c r="E6" s="11" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Boundary</t>
         </is>
       </c>
       <c r="F6" s="11" t="inlineStr">
         <is>
-          <t>Acceptance Criteria</t>
+          <t>Code</t>
         </is>
       </c>
     </row>
@@ -631,17 +626,17 @@
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>A full event's list shows every place taken against the capacity and the number on the waiting list, not counting withdrawals</t>
+          <t>The open list shows a new registration and then its withdrawal within 15 seconds, without refreshing the page</t>
         </is>
       </c>
       <c r="D7" s="11" t="inlineStr">
         <is>
-          <t>AC5</t>
+          <t>AC6, AC5</t>
         </is>
       </c>
       <c r="E7" s="11" t="inlineStr">
         <is>
-          <t>Boundary</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="F7" s="11" t="inlineStr">
@@ -663,12 +658,12 @@
       </c>
       <c r="C8" s="11" t="inlineStr">
         <is>
-          <t>Checked-in attendees of a past event are shown as Attended, apart from those who registered but did not come and those who withdrew</t>
+          <t>When registration is not enabled, the list says so instead of showing an empty list</t>
         </is>
       </c>
       <c r="D8" s="11" t="inlineStr">
         <is>
-          <t>AC3, AC5</t>
+          <t>AC7</t>
         </is>
       </c>
       <c r="E8" s="11" t="inlineStr">
@@ -695,12 +690,12 @@
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>An event with no capacity limit shows how many are registered and says there is no limit</t>
+          <t>When registration was turned off after someone registered, the list says it is not enabled and still lists that attendee</t>
         </is>
       </c>
       <c r="D9" s="11" t="inlineStr">
         <is>
-          <t>AC5</t>
+          <t>AC7</t>
         </is>
       </c>
       <c r="E9" s="11" t="inlineStr">
@@ -727,22 +722,22 @@
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
-          <t>An event with registration open and nobody registered says no one has registered yet, with no places taken</t>
+          <t>The coordinator assigned to the event opens its Attendees tab and sees its registrations and places taken</t>
         </is>
       </c>
       <c r="D10" s="11" t="inlineStr">
         <is>
-          <t>AC5</t>
+          <t>AC1</t>
         </is>
       </c>
       <c r="E10" s="11" t="inlineStr">
         <is>
-          <t>Boundary</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="F10" s="11" t="inlineStr">
         <is>
-          <t>Code</t>
+          <t>Acceptance Criteria</t>
         </is>
       </c>
     </row>
@@ -759,17 +754,17 @@
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>The open list shows a new registration and then its withdrawal within 15 seconds, without refreshing the page</t>
+          <t>An organiser at the same client who did not raise the event can open the event but not its registration list</t>
         </is>
       </c>
       <c r="D11" s="11" t="inlineStr">
         <is>
-          <t>AC6, AC5</t>
+          <t>AC8</t>
         </is>
       </c>
       <c r="E11" s="11" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="F11" s="11" t="inlineStr">
@@ -791,17 +786,17 @@
       </c>
       <c r="C12" s="11" t="inlineStr">
         <is>
-          <t>When registration is not enabled, the list says so instead of showing an empty list</t>
+          <t>An organiser from another client cannot open the registration list even by typing its address</t>
         </is>
       </c>
       <c r="D12" s="11" t="inlineStr">
         <is>
-          <t>AC7</t>
+          <t>AC8</t>
         </is>
       </c>
       <c r="E12" s="11" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="F12" s="11" t="inlineStr">
@@ -823,17 +818,17 @@
       </c>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t>When registration was turned off after someone registered, the list says it is not enabled and still lists that attendee</t>
+          <t>A coordinator who is not assigned to the event cannot view its registration list</t>
         </is>
       </c>
       <c r="D13" s="11" t="inlineStr">
         <is>
-          <t>AC7</t>
+          <t>AC1</t>
         </is>
       </c>
       <c r="E13" s="11" t="inlineStr">
         <is>
-          <t>Boundary</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="F13" s="11" t="inlineStr">
@@ -855,17 +850,17 @@
       </c>
       <c r="C14" s="11" t="inlineStr">
         <is>
-          <t>The coordinator assigned to the event opens its Attendees tab and sees the same list as the organiser</t>
+          <t>An attendee registered for the event has no Attendees tab and cannot open the list by typing its address</t>
         </is>
       </c>
       <c r="D14" s="11" t="inlineStr">
         <is>
-          <t>AC1</t>
+          <t>AC9</t>
         </is>
       </c>
       <c r="E14" s="11" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="F14" s="11" t="inlineStr">
@@ -887,12 +882,12 @@
       </c>
       <c r="C15" s="11" t="inlineStr">
         <is>
-          <t>An organiser at the same client who did not raise the event can open the event but not its registration list</t>
+          <t>Venue Staff and Technical Support Staff have no Attendees tab and cannot open the list by typing its address</t>
         </is>
       </c>
       <c r="D15" s="11" t="inlineStr">
         <is>
-          <t>AC8</t>
+          <t>AC9</t>
         </is>
       </c>
       <c r="E15" s="11" t="inlineStr">
@@ -906,224 +901,169 @@
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="10" t="inlineStr">
-        <is>
-          <t>TC13</t>
-        </is>
-      </c>
-      <c r="B16" s="11" t="inlineStr">
-        <is>
-          <t>SPM-65-TC13</t>
-        </is>
-      </c>
-      <c r="C16" s="11" t="inlineStr">
-        <is>
-          <t>An organiser from another client cannot open the registration list even by typing its address</t>
-        </is>
-      </c>
-      <c r="D16" s="11" t="inlineStr">
-        <is>
-          <t>AC8</t>
-        </is>
-      </c>
-      <c r="E16" s="11" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="F16" s="11" t="inlineStr">
-        <is>
-          <t>Acceptance Criteria</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="10" t="inlineStr">
-        <is>
-          <t>TC14</t>
-        </is>
-      </c>
-      <c r="B17" s="11" t="inlineStr">
-        <is>
-          <t>SPM-65-TC14</t>
-        </is>
-      </c>
-      <c r="C17" s="11" t="inlineStr">
-        <is>
-          <t>A coordinator who is not assigned to the event cannot view its registration list</t>
-        </is>
-      </c>
-      <c r="D17" s="11" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>Acceptance Criterion</t>
+        </is>
+      </c>
+      <c r="C18" s="8" t="n"/>
+      <c r="D18" s="9" t="n"/>
+      <c r="E18" s="7" t="inlineStr">
+        <is>
+          <t>Covered by</t>
+        </is>
+      </c>
+      <c r="F18" s="9" t="n"/>
+    </row>
+    <row r="19" ht="44.5" customHeight="1">
+      <c r="A19" s="11" t="inlineStr">
         <is>
           <t>AC1</t>
         </is>
       </c>
-      <c r="E17" s="11" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="F17" s="11" t="inlineStr">
-        <is>
-          <t>Code</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="10" t="inlineStr">
-        <is>
-          <t>TC15</t>
-        </is>
-      </c>
-      <c r="B18" s="11" t="inlineStr">
-        <is>
-          <t>SPM-65-TC15</t>
-        </is>
-      </c>
-      <c r="C18" s="11" t="inlineStr">
-        <is>
-          <t>An attendee registered for the event has no Attendees tab and cannot open the list by typing its address</t>
-        </is>
-      </c>
-      <c r="D18" s="11" t="inlineStr">
-        <is>
-          <t>AC9</t>
-        </is>
-      </c>
-      <c r="E18" s="11" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="F18" s="11" t="inlineStr">
-        <is>
-          <t>Acceptance Criteria</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="10" t="inlineStr">
-        <is>
-          <t>TC16</t>
-        </is>
-      </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t>SPM-65-TC16</t>
-        </is>
-      </c>
-      <c r="C19" s="11" t="inlineStr">
-        <is>
-          <t>Venue Staff and Technical Support Staff have no Attendees tab and cannot open the list by typing its address</t>
-        </is>
-      </c>
-      <c r="D19" s="11" t="inlineStr">
-        <is>
-          <t>AC9</t>
-        </is>
-      </c>
+          <t>The responsible Event Organiser and the assigned Event Coordinator can view the list of registrations for their event.</t>
+        </is>
+      </c>
+      <c r="C19" s="8" t="n"/>
+      <c r="D19" s="9" t="n"/>
       <c r="E19" s="11" t="inlineStr">
         <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="F19" s="11" t="inlineStr">
-        <is>
-          <t>Acceptance Criteria</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="10" t="inlineStr">
-        <is>
-          <t>TC17</t>
+          <t>SPM-65-TC01
+SPM-65-TC07
+SPM-65-TC10</t>
+        </is>
+      </c>
+      <c r="F19" s="9" t="n"/>
+    </row>
+    <row r="20" ht="31" customHeight="1">
+      <c r="A20" s="11" t="inlineStr">
+        <is>
+          <t>AC2</t>
         </is>
       </c>
       <c r="B20" s="11" t="inlineStr">
         <is>
-          <t>SPM-65-TC17</t>
-        </is>
-      </c>
-      <c r="C20" s="11" t="inlineStr">
-        <is>
-          <t>The Operations Manager and the Safety Officer have no Attendees tab and cannot open the registration list</t>
-        </is>
-      </c>
-      <c r="D20" s="11" t="inlineStr">
-        <is>
-          <t>AC9</t>
-        </is>
-      </c>
+          <t>Each entry shows the attendee's name, contact details, registration status and registration date.</t>
+        </is>
+      </c>
+      <c r="C20" s="8" t="n"/>
+      <c r="D20" s="9" t="n"/>
       <c r="E20" s="11" t="inlineStr">
         <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="F20" s="11" t="inlineStr">
-        <is>
-          <t>Code</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="7" t="inlineStr">
-        <is>
-          <t>AC</t>
-        </is>
-      </c>
-      <c r="B23" s="7" t="inlineStr">
-        <is>
-          <t>Acceptance Criterion</t>
+          <t>SPM-65-TC01</t>
+        </is>
+      </c>
+      <c r="F20" s="9" t="n"/>
+    </row>
+    <row r="21" ht="31" customHeight="1">
+      <c r="A21" s="11" t="inlineStr">
+        <is>
+          <t>AC3</t>
+        </is>
+      </c>
+      <c r="B21" s="11" t="inlineStr">
+        <is>
+          <t>Registered, waitlisted, withdrawn and checked-in attendees are distinguishable.</t>
+        </is>
+      </c>
+      <c r="C21" s="8" t="n"/>
+      <c r="D21" s="9" t="n"/>
+      <c r="E21" s="11" t="inlineStr">
+        <is>
+          <t>SPM-65-TC01
+SPM-65-TC02</t>
+        </is>
+      </c>
+      <c r="F21" s="9" t="n"/>
+    </row>
+    <row r="22" ht="31" customHeight="1">
+      <c r="A22" s="11" t="inlineStr">
+        <is>
+          <t>AC4</t>
+        </is>
+      </c>
+      <c r="B22" s="11" t="inlineStr">
+        <is>
+          <t>Attendees added manually on the Organiser's behalf are identifiable (see: Manually Add Attendee).</t>
+        </is>
+      </c>
+      <c r="C22" s="8" t="n"/>
+      <c r="D22" s="9" t="n"/>
+      <c r="E22" s="11" t="inlineStr">
+        <is>
+          <t>SPM-65-TC01</t>
+        </is>
+      </c>
+      <c r="F22" s="9" t="n"/>
+    </row>
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" s="11" t="inlineStr">
+        <is>
+          <t>AC5</t>
+        </is>
+      </c>
+      <c r="B23" s="11" t="inlineStr">
+        <is>
+          <t>The list shows the number of active registrations against the registration capacity, and the number of attendees on the waiting list.</t>
         </is>
       </c>
       <c r="C23" s="8" t="n"/>
       <c r="D23" s="9" t="n"/>
-      <c r="E23" s="7" t="inlineStr">
-        <is>
-          <t>Covered by</t>
+      <c r="E23" s="11" t="inlineStr">
+        <is>
+          <t>SPM-65-TC01
+SPM-65-TC02
+SPM-65-TC03
+SPM-65-TC04</t>
         </is>
       </c>
       <c r="F23" s="9" t="n"/>
     </row>
-    <row r="24" ht="44.5" customHeight="1">
+    <row r="24" ht="31" customHeight="1">
       <c r="A24" s="11" t="inlineStr">
         <is>
-          <t>AC1</t>
+          <t>AC6</t>
         </is>
       </c>
       <c r="B24" s="11" t="inlineStr">
         <is>
-          <t>The responsible Event Organiser and the assigned Event Coordinator can view the list of registrations for their event.</t>
+          <t>The list reflects registrations, withdrawals and waiting-list changes as they happen.</t>
         </is>
       </c>
       <c r="C24" s="8" t="n"/>
       <c r="D24" s="9" t="n"/>
       <c r="E24" s="11" t="inlineStr">
         <is>
-          <t>SPM-65-TC01
-SPM-65-TC11
-SPM-65-TC14</t>
+          <t>SPM-65-TC04</t>
         </is>
       </c>
       <c r="F24" s="9" t="n"/>
     </row>
-    <row r="25" ht="31" customHeight="1">
+    <row r="25" ht="44.5" customHeight="1">
       <c r="A25" s="11" t="inlineStr">
         <is>
-          <t>AC2</t>
+          <t>AC7</t>
         </is>
       </c>
       <c r="B25" s="11" t="inlineStr">
         <is>
-          <t>Each entry shows the attendee's name, contact details, registration status and registration date.</t>
+          <t>Given registration is not enabled for the event, when the list is opened, then it states that registration is not enabled rather than showing an empty list.</t>
         </is>
       </c>
       <c r="C25" s="8" t="n"/>
       <c r="D25" s="9" t="n"/>
       <c r="E25" s="11" t="inlineStr">
         <is>
-          <t>SPM-65-TC01</t>
+          <t>SPM-65-TC05
+SPM-65-TC06</t>
         </is>
       </c>
       <c r="F25" s="9" t="n"/>
@@ -1131,20 +1071,20 @@
     <row r="26" ht="31" customHeight="1">
       <c r="A26" s="11" t="inlineStr">
         <is>
-          <t>AC3</t>
+          <t>AC8</t>
         </is>
       </c>
       <c r="B26" s="11" t="inlineStr">
         <is>
-          <t>Registered, waitlisted, withdrawn and checked-in attendees are distinguishable.</t>
+          <t>An Event Organiser cannot view the registration list of an event they are not responsible for.</t>
         </is>
       </c>
       <c r="C26" s="8" t="n"/>
       <c r="D26" s="9" t="n"/>
       <c r="E26" s="11" t="inlineStr">
         <is>
-          <t>SPM-65-TC02
-SPM-65-TC05</t>
+          <t>SPM-65-TC08
+SPM-65-TC09</t>
         </is>
       </c>
       <c r="F26" s="9" t="n"/>
@@ -1152,138 +1092,31 @@
     <row r="27" ht="31" customHeight="1">
       <c r="A27" s="11" t="inlineStr">
         <is>
-          <t>AC4</t>
+          <t>AC9</t>
         </is>
       </c>
       <c r="B27" s="11" t="inlineStr">
         <is>
-          <t>Attendees added manually on the Organiser's behalf are identifiable (see: Manually Add Attendee).</t>
+          <t>Attendees, Venue Staff and Technical Support Staff cannot view the registration list.</t>
         </is>
       </c>
       <c r="C27" s="8" t="n"/>
       <c r="D27" s="9" t="n"/>
       <c r="E27" s="11" t="inlineStr">
         <is>
-          <t>SPM-65-TC03</t>
+          <t>SPM-65-TC11
+SPM-65-TC12</t>
         </is>
       </c>
       <c r="F27" s="9" t="n"/>
     </row>
-    <row r="28" ht="71.5" customHeight="1">
-      <c r="A28" s="11" t="inlineStr">
-        <is>
-          <t>AC5</t>
-        </is>
-      </c>
-      <c r="B28" s="11" t="inlineStr">
-        <is>
-          <t>The list shows the number of active registrations against the registration capacity, and the number of attendees on the waiting list.</t>
-        </is>
-      </c>
-      <c r="C28" s="8" t="n"/>
-      <c r="D28" s="9" t="n"/>
-      <c r="E28" s="11" t="inlineStr">
-        <is>
-          <t>SPM-65-TC04
-SPM-65-TC05
-SPM-65-TC06
-SPM-65-TC07
-SPM-65-TC08</t>
-        </is>
-      </c>
-      <c r="F28" s="9" t="n"/>
-    </row>
-    <row r="29" ht="31" customHeight="1">
-      <c r="A29" s="11" t="inlineStr">
-        <is>
-          <t>AC6</t>
+    <row r="29" ht="179.5" customHeight="1">
+      <c r="A29" s="7" t="inlineStr">
+        <is>
+          <t>Code reviewed</t>
         </is>
       </c>
       <c r="B29" s="11" t="inlineStr">
-        <is>
-          <t>The list reflects registrations, withdrawals and waiting-list changes as they happen.</t>
-        </is>
-      </c>
-      <c r="C29" s="8" t="n"/>
-      <c r="D29" s="9" t="n"/>
-      <c r="E29" s="11" t="inlineStr">
-        <is>
-          <t>SPM-65-TC08</t>
-        </is>
-      </c>
-      <c r="F29" s="9" t="n"/>
-    </row>
-    <row r="30" ht="44.5" customHeight="1">
-      <c r="A30" s="11" t="inlineStr">
-        <is>
-          <t>AC7</t>
-        </is>
-      </c>
-      <c r="B30" s="11" t="inlineStr">
-        <is>
-          <t>Given registration is not enabled for the event, when the list is opened, then it states that registration is not enabled rather than showing an empty list.</t>
-        </is>
-      </c>
-      <c r="C30" s="8" t="n"/>
-      <c r="D30" s="9" t="n"/>
-      <c r="E30" s="11" t="inlineStr">
-        <is>
-          <t>SPM-65-TC09
-SPM-65-TC10</t>
-        </is>
-      </c>
-      <c r="F30" s="9" t="n"/>
-    </row>
-    <row r="31" ht="31" customHeight="1">
-      <c r="A31" s="11" t="inlineStr">
-        <is>
-          <t>AC8</t>
-        </is>
-      </c>
-      <c r="B31" s="11" t="inlineStr">
-        <is>
-          <t>An Event Organiser cannot view the registration list of an event they are not responsible for.</t>
-        </is>
-      </c>
-      <c r="C31" s="8" t="n"/>
-      <c r="D31" s="9" t="n"/>
-      <c r="E31" s="11" t="inlineStr">
-        <is>
-          <t>SPM-65-TC12
-SPM-65-TC13</t>
-        </is>
-      </c>
-      <c r="F31" s="9" t="n"/>
-    </row>
-    <row r="32" ht="44.5" customHeight="1">
-      <c r="A32" s="11" t="inlineStr">
-        <is>
-          <t>AC9</t>
-        </is>
-      </c>
-      <c r="B32" s="11" t="inlineStr">
-        <is>
-          <t>Attendees, Venue Staff and Technical Support Staff cannot view the registration list.</t>
-        </is>
-      </c>
-      <c r="C32" s="8" t="n"/>
-      <c r="D32" s="9" t="n"/>
-      <c r="E32" s="11" t="inlineStr">
-        <is>
-          <t>SPM-65-TC15
-SPM-65-TC16
-SPM-65-TC17</t>
-        </is>
-      </c>
-      <c r="F32" s="9" t="n"/>
-    </row>
-    <row r="34" ht="179.5" customHeight="1">
-      <c r="A34" s="7" t="inlineStr">
-        <is>
-          <t>Code reviewed</t>
-        </is>
-      </c>
-      <c r="B34" s="11" t="inlineStr">
         <is>
           <t>src/app/api/events/[id]/registrations/route.ts
 src/app/events/[id]/attendees/page.tsx
@@ -1300,35 +1133,35 @@
 scripts/seed-spm65.ts</t>
         </is>
       </c>
-      <c r="C34" s="8" t="n"/>
-      <c r="D34" s="8" t="n"/>
-      <c r="E34" s="8" t="n"/>
-      <c r="F34" s="9" t="n"/>
+      <c r="C29" s="8" t="n"/>
+      <c r="D29" s="8" t="n"/>
+      <c r="E29" s="8" t="n"/>
+      <c r="F29" s="9" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="22">
     <mergeCell ref="B23:D23"/>
     <mergeCell ref="E24:F24"/>
     <mergeCell ref="E23:F23"/>
-    <mergeCell ref="B29:D29"/>
-    <mergeCell ref="B28:D28"/>
-    <mergeCell ref="E29:F29"/>
-    <mergeCell ref="E28:F28"/>
-    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="E20:F20"/>
+    <mergeCell ref="E19:F19"/>
     <mergeCell ref="B1:F1"/>
-    <mergeCell ref="E31:F31"/>
     <mergeCell ref="B24:D24"/>
-    <mergeCell ref="E30:F30"/>
-    <mergeCell ref="B34:F34"/>
-    <mergeCell ref="B32:D32"/>
+    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="B29:F29"/>
     <mergeCell ref="B26:D26"/>
     <mergeCell ref="E27:F27"/>
     <mergeCell ref="E26:F26"/>
     <mergeCell ref="B25:D25"/>
-    <mergeCell ref="B31:D31"/>
-    <mergeCell ref="E32:F32"/>
     <mergeCell ref="E25:F25"/>
+    <mergeCell ref="B22:D22"/>
+    <mergeCell ref="B18:D18"/>
     <mergeCell ref="B27:D27"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="E21:F21"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A4" r:id="rId1"/>
@@ -1343,11 +1176,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A13" r:id="rId10"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A14" r:id="rId11"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A15" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A16" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A17" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A18" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A19" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A20" r:id="rId17"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1394,7 +1222,7 @@
       </c>
       <c r="B3" s="13" t="inlineStr">
         <is>
-          <t>When registration is not enabled, the list says so instead of showing an empty list</t>
+          <t>An organiser from another client cannot open the registration list even by typing its address</t>
         </is>
       </c>
     </row>
@@ -1412,7 +1240,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="44.5" customHeight="1">
+    <row r="5" ht="152.5" customHeight="1">
       <c r="A5" s="12" t="inlineStr">
         <is>
           <t>Test Steps</t>
@@ -1421,8 +1249,10 @@
       <c r="B5" s="13" t="inlineStr">
         <is>
           <t>1. Click 'My Events' in the sidebar
-2. Click 'SPM65 Closed Doors Gala' in the list
-3. Click the 'Attendees' tab</t>
+2. Click 'SPM65 Harbourfront Seminar' in the list
+3. Note the event's reference from the browser address bar (the part after /events/, starting EVT-)
+4. Log out and log in as Rachel Ng (rachel.ng@meridianfina.com / password123), an Event Organiser at Meridian Financial Group
+5. Type /events/&lt;reference from step 3&gt;/attendees after the site address in the browser address bar (e.g. http://localhost:3000/events/&lt;reference from step 3&gt;/attendees) and press Enter</t>
         </is>
       </c>
     </row>
@@ -1434,11 +1264,11 @@
       </c>
       <c r="B6" s="13" t="inlineStr">
         <is>
-          <t>Event: SPM65 Closed Doors Gala (registration not enabled, no registrations)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="58" customHeight="1">
+          <t>Event: SPM65 Harbourfront Seminar (Straits Medical Institute) | Organiser: Rachel Ng (Meridian Financial Group)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="44.5" customHeight="1">
       <c r="A7" s="12" t="inlineStr">
         <is>
           <t>Expected Result</t>
@@ -1446,7 +1276,7 @@
       </c>
       <c r="B7" s="13" t="inlineStr">
         <is>
-          <t>Step 3: A blue message says 'Registration is not enabled for this event' and 'Attendees can't register until the coordinator turns registration on.' There is no table, no 'No one has registered yet' message, and no '… places taken' line.</t>
+          <t>Step 5: The page says 'This event doesn't exist, or you don't have access to it.' No event title, attendee names or places taken are shown.</t>
         </is>
       </c>
     </row>
@@ -1567,11 +1397,11 @@
       </c>
       <c r="B3" s="13" t="inlineStr">
         <is>
-          <t>When registration was turned off after someone registered, the list says it is not enabled and still lists that attendee</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="71.5" customHeight="1">
+          <t>A coordinator who is not assigned to the event cannot view its registration list</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="85" customHeight="1">
       <c r="A4" s="12" t="inlineStr">
         <is>
           <t>Pre-conditions</t>
@@ -1580,7 +1410,7 @@
       <c r="B4" s="13" t="inlineStr">
         <is>
           <t>Test data loaded: `npm run fixtures:spm65` has been run since the last full `npx prisma db seed`.
-Logged in as Evelyn Chen (evelyn.chen@straitsmedic.com / password123).
+Logged in as Priya Raj (priya.raj@connectsphere.com / password123), an Event Coordinator who is not assigned to any 'SPM65 …' event.
 Nothing is saved in this case.</t>
         </is>
       </c>
@@ -1593,8 +1423,8 @@
       </c>
       <c r="B5" s="13" t="inlineStr">
         <is>
-          <t>1. Click 'My Events' in the sidebar
-2. Click 'SPM65 Paused Forum' in the list
+          <t>1. Click 'All Events' in the sidebar
+2. Click 'SPM65 Harbourfront Seminar' in the list
 3. Click the 'Attendees' tab</t>
         </is>
       </c>
@@ -1607,11 +1437,11 @@
       </c>
       <c r="B6" s="13" t="inlineStr">
         <is>
-          <t>Event: SPM65 Paused Forum (registration turned off, capacity 20) | Registered: Marcus Yeo</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="58" customHeight="1">
+          <t>Event: SPM65 Harbourfront Seminar (assigned to Daniel Tan) | Coordinator: Priya Raj (not assigned)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="44.5" customHeight="1">
       <c r="A7" s="12" t="inlineStr">
         <is>
           <t>Expected Result</t>
@@ -1619,7 +1449,7 @@
       </c>
       <c r="B7" s="13" t="inlineStr">
         <is>
-          <t>Step 3: A blue message says 'Registration is not enabled for this event'. Under it, it says '1 of 20 places taken · 0 on the waiting list', and the table lists Marcus Yeo, marcus.yeo@example.com, 'Registered', 2 Oct 2026, 10:00.</t>
+          <t>Step 3: A red message 'Not authorised' says 'You can only view the registrations for events you are responsible for.' No attendee names, emails or places taken are shown.</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1570,7 @@
       </c>
       <c r="B3" s="13" t="inlineStr">
         <is>
-          <t>The coordinator assigned to the event opens its Attendees tab and sees the same list as the organiser</t>
+          <t>An attendee registered for the event has no Attendees tab and cannot open the list by typing its address</t>
         </is>
       </c>
     </row>
@@ -1753,12 +1583,12 @@
       <c r="B4" s="13" t="inlineStr">
         <is>
           <t>Test data loaded: `npm run fixtures:spm65` has been run since the last full `npx prisma db seed`.
-Logged in as Daniel Tan (daniel.tan@connectsphere.com / password123), the coordinator assigned to every 'SPM65 …' event.
+Logged in as Marcus Yeo (marcus.yeo@example.com / password123), an Attendee registered for 'SPM65 Harbourfront Seminar'.
 Nothing is saved in this case.</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="44.5" customHeight="1">
+    <row r="5" ht="112" customHeight="1">
       <c r="A5" s="12" t="inlineStr">
         <is>
           <t>Test Steps</t>
@@ -1766,9 +1596,10 @@
       </c>
       <c r="B5" s="13" t="inlineStr">
         <is>
-          <t>1. Click 'All Events' in the sidebar
-2. Click 'SPM65 Harbourfront Seminar' in the list
-3. Click the 'Attendees' tab</t>
+          <t>1. Click 'Browse Events' in the sidebar
+2. Click 'SPM65 Harbourfront Seminar'
+3. Note the event's reference from the browser address bar (the part after /events/, starting EVT-)
+4. Type /events/&lt;reference from step 3&gt;/attendees after the site address in the browser address bar (e.g. http://localhost:3000/events/&lt;reference from step 3&gt;/attendees) and press Enter</t>
         </is>
       </c>
     </row>
@@ -1780,11 +1611,11 @@
       </c>
       <c r="B6" s="13" t="inlineStr">
         <is>
-          <t>Event: SPM65 Harbourfront Seminar | Coordinator: Daniel Tan</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="98.5" customHeight="1">
+          <t>Event: SPM65 Harbourfront Seminar | Attendee: Marcus Yeo</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
       <c r="A7" s="12" t="inlineStr">
         <is>
           <t>Expected Result</t>
@@ -1792,8 +1623,8 @@
       </c>
       <c r="B7" s="13" t="inlineStr">
         <is>
-          <t>Step 2: The event page shows the tabs 'Overview', 'Venue', 'Equipment', 'Attendees' and 'Readiness'.
-Step 3: The Attendees page says '3 of 3 places taken · 1 on the waiting list' and lists Marcus Yeo, Farhan Ismail, Anita Devi (with 'Added by Evelyn Chen'), Tom Harris and Siti Nurhaliza, with the same emails, badges and dates as the organiser sees.</t>
+          <t>Step 2: The event page opens. There is no 'Attendees' tab.
+Step 4: A red message 'Not authorised' says 'You can only view the registrations for events you are responsible for.' No other attendee's name or email is shown.</t>
         </is>
       </c>
     </row>
@@ -1914,703 +1745,6 @@
       </c>
       <c r="B3" s="13" t="inlineStr">
         <is>
-          <t>An organiser at the same client who did not raise the event can open the event but not its registration list</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="85" customHeight="1">
-      <c r="A4" s="12" t="inlineStr">
-        <is>
-          <t>Pre-conditions</t>
-        </is>
-      </c>
-      <c r="B4" s="13" t="inlineStr">
-        <is>
-          <t>Test data loaded: `npm run fixtures:spm65` has been run since the last full `npx prisma db seed`.
-Logged in as Raj Kumar (raj.kumar@straitsmedic.com / password123), an Event Organiser at Straits Medical Institute, the same client as Evelyn Chen, who organised the event.
-Nothing is saved in this case.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="44.5" customHeight="1">
-      <c r="A5" s="12" t="inlineStr">
-        <is>
-          <t>Test Steps</t>
-        </is>
-      </c>
-      <c r="B5" s="13" t="inlineStr">
-        <is>
-          <t>1. Click 'My Events' in the sidebar
-2. Click 'SPM65 Harbourfront Seminar' in the list
-3. Click the 'Attendees' tab</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="31" customHeight="1">
-      <c r="A6" s="12" t="inlineStr">
-        <is>
-          <t>Test Data</t>
-        </is>
-      </c>
-      <c r="B6" s="13" t="inlineStr">
-        <is>
-          <t>Event: SPM65 Harbourfront Seminar (organised by Evelyn Chen) | Organiser: Raj Kumar (same client, not responsible)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="71.5" customHeight="1">
-      <c r="A7" s="12" t="inlineStr">
-        <is>
-          <t>Expected Result</t>
-        </is>
-      </c>
-      <c r="B7" s="13" t="inlineStr">
-        <is>
-          <t>Step 2: The event page 'SPM65 Harbourfront Seminar' opens, with an 'Attendees' tab.
-Step 3: A red message 'Not authorised' says 'You can only view the registrations for events you are responsible for.' No attendee names, emails or places taken are shown.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="17.5" customHeight="1">
-      <c r="A8" s="12" t="inlineStr">
-        <is>
-          <t>Created By</t>
-        </is>
-      </c>
-      <c r="B8" s="13" t="inlineStr">
-        <is>
-          <t>Sammi Chua</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="12" t="inlineStr">
-        <is>
-          <t>Creation Date</t>
-        </is>
-      </c>
-      <c r="B9" s="14" t="n">
-        <v>46310</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>Item</t>
-        </is>
-      </c>
-      <c r="B11" s="5" t="n"/>
-      <c r="C11" s="6" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="3" t="inlineStr">
-        <is>
-          <t>Actual Result</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="3" t="inlineStr">
-        <is>
-          <t>Pass/Fail/Not Executed/Blocked</t>
-        </is>
-      </c>
-      <c r="B13" s="3" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="3" t="inlineStr">
-        <is>
-          <t>Remarks</t>
-        </is>
-      </c>
-      <c r="B14" s="3" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t>Executed by</t>
-        </is>
-      </c>
-      <c r="B15" s="3" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="3" t="inlineStr">
-        <is>
-          <t>Date of Execution</t>
-        </is>
-      </c>
-      <c r="B16" s="3" t="n"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="0" summaryRight="0"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C16"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
-  <cols>
-    <col width="24.77734375" customWidth="1" min="1" max="1"/>
-    <col width="56.77734375" customWidth="1" min="2" max="2"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Item</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="n"/>
-    </row>
-    <row r="2" ht="17.5" customHeight="1">
-      <c r="A2" s="12" t="inlineStr">
-        <is>
-          <t>Test Case ID</t>
-        </is>
-      </c>
-      <c r="B2" s="13" t="inlineStr">
-        <is>
-          <t>SPM-65-TC13</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="31" customHeight="1">
-      <c r="A3" s="12" t="inlineStr">
-        <is>
-          <t>Summary</t>
-        </is>
-      </c>
-      <c r="B3" s="13" t="inlineStr">
-        <is>
-          <t>An organiser from another client cannot open the registration list even by typing its address</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="71.5" customHeight="1">
-      <c r="A4" s="12" t="inlineStr">
-        <is>
-          <t>Pre-conditions</t>
-        </is>
-      </c>
-      <c r="B4" s="13" t="inlineStr">
-        <is>
-          <t>Test data loaded: `npm run fixtures:spm65` has been run since the last full `npx prisma db seed`.
-Logged in as Evelyn Chen (evelyn.chen@straitsmedic.com / password123).
-Nothing is saved in this case.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="152.5" customHeight="1">
-      <c r="A5" s="12" t="inlineStr">
-        <is>
-          <t>Test Steps</t>
-        </is>
-      </c>
-      <c r="B5" s="13" t="inlineStr">
-        <is>
-          <t>1. Click 'My Events' in the sidebar
-2. Click 'SPM65 Harbourfront Seminar' in the list
-3. Note the event's reference from the browser address bar (the part after /events/, starting EVT-)
-4. Log out and log in as Rachel Ng (rachel.ng@meridianfina.com / password123), an Event Organiser at Meridian Financial Group
-5. Type /events/&lt;reference from step 3&gt;/attendees after the site address in the browser address bar (e.g. http://localhost:3000/events/&lt;reference from step 3&gt;/attendees) and press Enter</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="31" customHeight="1">
-      <c r="A6" s="12" t="inlineStr">
-        <is>
-          <t>Test Data</t>
-        </is>
-      </c>
-      <c r="B6" s="13" t="inlineStr">
-        <is>
-          <t>Event: SPM65 Harbourfront Seminar (Straits Medical Institute) | Organiser: Rachel Ng (Meridian Financial Group)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="44.5" customHeight="1">
-      <c r="A7" s="12" t="inlineStr">
-        <is>
-          <t>Expected Result</t>
-        </is>
-      </c>
-      <c r="B7" s="13" t="inlineStr">
-        <is>
-          <t>Step 5: The page says 'This event doesn't exist, or you don't have access to it.' No event title, attendee names or places taken are shown.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="17.5" customHeight="1">
-      <c r="A8" s="12" t="inlineStr">
-        <is>
-          <t>Created By</t>
-        </is>
-      </c>
-      <c r="B8" s="13" t="inlineStr">
-        <is>
-          <t>Sammi Chua</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="12" t="inlineStr">
-        <is>
-          <t>Creation Date</t>
-        </is>
-      </c>
-      <c r="B9" s="14" t="n">
-        <v>46310</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>Item</t>
-        </is>
-      </c>
-      <c r="B11" s="5" t="n"/>
-      <c r="C11" s="6" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="3" t="inlineStr">
-        <is>
-          <t>Actual Result</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="3" t="inlineStr">
-        <is>
-          <t>Pass/Fail/Not Executed/Blocked</t>
-        </is>
-      </c>
-      <c r="B13" s="3" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="3" t="inlineStr">
-        <is>
-          <t>Remarks</t>
-        </is>
-      </c>
-      <c r="B14" s="3" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t>Executed by</t>
-        </is>
-      </c>
-      <c r="B15" s="3" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="3" t="inlineStr">
-        <is>
-          <t>Date of Execution</t>
-        </is>
-      </c>
-      <c r="B16" s="3" t="n"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="0" summaryRight="0"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C16"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
-  <cols>
-    <col width="24.77734375" customWidth="1" min="1" max="1"/>
-    <col width="56.77734375" customWidth="1" min="2" max="2"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Item</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="n"/>
-    </row>
-    <row r="2" ht="17.5" customHeight="1">
-      <c r="A2" s="12" t="inlineStr">
-        <is>
-          <t>Test Case ID</t>
-        </is>
-      </c>
-      <c r="B2" s="13" t="inlineStr">
-        <is>
-          <t>SPM-65-TC14</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="31" customHeight="1">
-      <c r="A3" s="12" t="inlineStr">
-        <is>
-          <t>Summary</t>
-        </is>
-      </c>
-      <c r="B3" s="13" t="inlineStr">
-        <is>
-          <t>A coordinator who is not assigned to the event cannot view its registration list</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="85" customHeight="1">
-      <c r="A4" s="12" t="inlineStr">
-        <is>
-          <t>Pre-conditions</t>
-        </is>
-      </c>
-      <c r="B4" s="13" t="inlineStr">
-        <is>
-          <t>Test data loaded: `npm run fixtures:spm65` has been run since the last full `npx prisma db seed`.
-Logged in as Priya Raj (priya.raj@connectsphere.com / password123), an Event Coordinator who is not assigned to any 'SPM65 …' event.
-Nothing is saved in this case.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="44.5" customHeight="1">
-      <c r="A5" s="12" t="inlineStr">
-        <is>
-          <t>Test Steps</t>
-        </is>
-      </c>
-      <c r="B5" s="13" t="inlineStr">
-        <is>
-          <t>1. Click 'All Events' in the sidebar
-2. Click 'SPM65 Harbourfront Seminar' in the list
-3. Click the 'Attendees' tab</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="31" customHeight="1">
-      <c r="A6" s="12" t="inlineStr">
-        <is>
-          <t>Test Data</t>
-        </is>
-      </c>
-      <c r="B6" s="13" t="inlineStr">
-        <is>
-          <t>Event: SPM65 Harbourfront Seminar (assigned to Daniel Tan) | Coordinator: Priya Raj (not assigned)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="44.5" customHeight="1">
-      <c r="A7" s="12" t="inlineStr">
-        <is>
-          <t>Expected Result</t>
-        </is>
-      </c>
-      <c r="B7" s="13" t="inlineStr">
-        <is>
-          <t>Step 3: A red message 'Not authorised' says 'You can only view the registrations for events you are responsible for.' No attendee names, emails or places taken are shown.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="17.5" customHeight="1">
-      <c r="A8" s="12" t="inlineStr">
-        <is>
-          <t>Created By</t>
-        </is>
-      </c>
-      <c r="B8" s="13" t="inlineStr">
-        <is>
-          <t>Sammi Chua</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="12" t="inlineStr">
-        <is>
-          <t>Creation Date</t>
-        </is>
-      </c>
-      <c r="B9" s="14" t="n">
-        <v>46310</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>Item</t>
-        </is>
-      </c>
-      <c r="B11" s="5" t="n"/>
-      <c r="C11" s="6" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="3" t="inlineStr">
-        <is>
-          <t>Actual Result</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="3" t="inlineStr">
-        <is>
-          <t>Pass/Fail/Not Executed/Blocked</t>
-        </is>
-      </c>
-      <c r="B13" s="3" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="3" t="inlineStr">
-        <is>
-          <t>Remarks</t>
-        </is>
-      </c>
-      <c r="B14" s="3" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t>Executed by</t>
-        </is>
-      </c>
-      <c r="B15" s="3" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="3" t="inlineStr">
-        <is>
-          <t>Date of Execution</t>
-        </is>
-      </c>
-      <c r="B16" s="3" t="n"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="0" summaryRight="0"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C16"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
-  <cols>
-    <col width="24.77734375" customWidth="1" min="1" max="1"/>
-    <col width="56.77734375" customWidth="1" min="2" max="2"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Item</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="n"/>
-    </row>
-    <row r="2" ht="17.5" customHeight="1">
-      <c r="A2" s="12" t="inlineStr">
-        <is>
-          <t>Test Case ID</t>
-        </is>
-      </c>
-      <c r="B2" s="13" t="inlineStr">
-        <is>
-          <t>SPM-65-TC15</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="31" customHeight="1">
-      <c r="A3" s="12" t="inlineStr">
-        <is>
-          <t>Summary</t>
-        </is>
-      </c>
-      <c r="B3" s="13" t="inlineStr">
-        <is>
-          <t>An attendee registered for the event has no Attendees tab and cannot open the list by typing its address</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="71.5" customHeight="1">
-      <c r="A4" s="12" t="inlineStr">
-        <is>
-          <t>Pre-conditions</t>
-        </is>
-      </c>
-      <c r="B4" s="13" t="inlineStr">
-        <is>
-          <t>Test data loaded: `npm run fixtures:spm65` has been run since the last full `npx prisma db seed`.
-Logged in as Marcus Yeo (marcus.yeo@example.com / password123), an Attendee registered for 'SPM65 Harbourfront Seminar'.
-Nothing is saved in this case.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="112" customHeight="1">
-      <c r="A5" s="12" t="inlineStr">
-        <is>
-          <t>Test Steps</t>
-        </is>
-      </c>
-      <c r="B5" s="13" t="inlineStr">
-        <is>
-          <t>1. Click 'Browse Events' in the sidebar
-2. Click 'SPM65 Harbourfront Seminar'
-3. Note the event's reference from the browser address bar (the part after /events/, starting EVT-)
-4. Type /events/&lt;reference from step 3&gt;/attendees after the site address in the browser address bar (e.g. http://localhost:3000/events/&lt;reference from step 3&gt;/attendees) and press Enter</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="17.5" customHeight="1">
-      <c r="A6" s="12" t="inlineStr">
-        <is>
-          <t>Test Data</t>
-        </is>
-      </c>
-      <c r="B6" s="13" t="inlineStr">
-        <is>
-          <t>Event: SPM65 Harbourfront Seminar | Attendee: Marcus Yeo</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="12" t="inlineStr">
-        <is>
-          <t>Expected Result</t>
-        </is>
-      </c>
-      <c r="B7" s="13" t="inlineStr">
-        <is>
-          <t>Step 2: The event page opens. There is no 'Attendees' tab.
-Step 4: A red message 'Not authorised' says 'You can only view the registrations for events you are responsible for.' No other attendee's name or email is shown.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="17.5" customHeight="1">
-      <c r="A8" s="12" t="inlineStr">
-        <is>
-          <t>Created By</t>
-        </is>
-      </c>
-      <c r="B8" s="13" t="inlineStr">
-        <is>
-          <t>Sammi Chua</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="12" t="inlineStr">
-        <is>
-          <t>Creation Date</t>
-        </is>
-      </c>
-      <c r="B9" s="14" t="n">
-        <v>46310</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>Item</t>
-        </is>
-      </c>
-      <c r="B11" s="5" t="n"/>
-      <c r="C11" s="6" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="3" t="inlineStr">
-        <is>
-          <t>Actual Result</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="3" t="inlineStr">
-        <is>
-          <t>Pass/Fail/Not Executed/Blocked</t>
-        </is>
-      </c>
-      <c r="B13" s="3" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="3" t="inlineStr">
-        <is>
-          <t>Remarks</t>
-        </is>
-      </c>
-      <c r="B14" s="3" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t>Executed by</t>
-        </is>
-      </c>
-      <c r="B15" s="3" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="3" t="inlineStr">
-        <is>
-          <t>Date of Execution</t>
-        </is>
-      </c>
-      <c r="B16" s="3" t="n"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="0" summaryRight="0"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C16"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
-  <cols>
-    <col width="24.77734375" customWidth="1" min="1" max="1"/>
-    <col width="56.77734375" customWidth="1" min="2" max="2"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Item</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="n"/>
-    </row>
-    <row r="2" ht="17.5" customHeight="1">
-      <c r="A2" s="12" t="inlineStr">
-        <is>
-          <t>Test Case ID</t>
-        </is>
-      </c>
-      <c r="B2" s="13" t="inlineStr">
-        <is>
-          <t>SPM-65-TC16</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="31" customHeight="1">
-      <c r="A3" s="12" t="inlineStr">
-        <is>
-          <t>Summary</t>
-        </is>
-      </c>
-      <c r="B3" s="13" t="inlineStr">
-        <is>
           <t>Venue Staff and Technical Support Staff have no Attendees tab and cannot open the list by typing its address</t>
         </is>
       </c>
@@ -2673,187 +1807,6 @@
 Step 6: A red message 'Not authorised' says 'You can only view the registrations for events you are responsible for.' No attendee names or emails are shown.
 Step 8: The event page opens with the tabs 'Overview' and 'Equipment'. There is no 'Attendees' tab.
 Step 9: A red message 'Not authorised' says 'You can only view the registrations for events you are responsible for.' No attendee names or emails are shown.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="17.5" customHeight="1">
-      <c r="A8" s="12" t="inlineStr">
-        <is>
-          <t>Created By</t>
-        </is>
-      </c>
-      <c r="B8" s="13" t="inlineStr">
-        <is>
-          <t>Sammi Chua</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="12" t="inlineStr">
-        <is>
-          <t>Creation Date</t>
-        </is>
-      </c>
-      <c r="B9" s="14" t="n">
-        <v>46310</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>Item</t>
-        </is>
-      </c>
-      <c r="B11" s="5" t="n"/>
-      <c r="C11" s="6" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="3" t="inlineStr">
-        <is>
-          <t>Actual Result</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="3" t="inlineStr">
-        <is>
-          <t>Pass/Fail/Not Executed/Blocked</t>
-        </is>
-      </c>
-      <c r="B13" s="3" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="3" t="inlineStr">
-        <is>
-          <t>Remarks</t>
-        </is>
-      </c>
-      <c r="B14" s="3" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t>Executed by</t>
-        </is>
-      </c>
-      <c r="B15" s="3" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="3" t="inlineStr">
-        <is>
-          <t>Date of Execution</t>
-        </is>
-      </c>
-      <c r="B16" s="3" t="n"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="0" summaryRight="0"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C16"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
-  <cols>
-    <col width="24.77734375" customWidth="1" min="1" max="1"/>
-    <col width="56.77734375" customWidth="1" min="2" max="2"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Item</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="n"/>
-    </row>
-    <row r="2" ht="17.5" customHeight="1">
-      <c r="A2" s="12" t="inlineStr">
-        <is>
-          <t>Test Case ID</t>
-        </is>
-      </c>
-      <c r="B2" s="13" t="inlineStr">
-        <is>
-          <t>SPM-65-TC17</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="31" customHeight="1">
-      <c r="A3" s="12" t="inlineStr">
-        <is>
-          <t>Summary</t>
-        </is>
-      </c>
-      <c r="B3" s="13" t="inlineStr">
-        <is>
-          <t>The Operations Manager and the Safety Officer have no Attendees tab and cannot open the registration list</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="71.5" customHeight="1">
-      <c r="A4" s="12" t="inlineStr">
-        <is>
-          <t>Pre-conditions</t>
-        </is>
-      </c>
-      <c r="B4" s="13" t="inlineStr">
-        <is>
-          <t>Test data loaded: `npm run fixtures:spm65` has been run since the last full `npx prisma db seed`.
-Logged in as Grace Lim (grace.lim@connectsphere.com / password123), the Operations Manager.
-Nothing is saved in this case.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="193" customHeight="1">
-      <c r="A5" s="12" t="inlineStr">
-        <is>
-          <t>Test Steps</t>
-        </is>
-      </c>
-      <c r="B5" s="13" t="inlineStr">
-        <is>
-          <t>1. Click 'All Events' in the sidebar
-2. Click 'SPM65 Harbourfront Seminar' in the list
-3. Note the event's reference from the browser address bar (the part after /events/, starting EVT-)
-4. Type /events/&lt;reference from step 3&gt;/attendees after the site address in the browser address bar (e.g. http://localhost:3000/events/&lt;reference from step 3&gt;/attendees) and press Enter
-5. Log out and log in as Hana Yusof (hana.yusof@connectsphere.com / password123), the Safety Officer
-6. Click 'All Events' in the sidebar
-7. Click 'SPM65 Harbourfront Seminar' in the list
-8. Type /events/&lt;reference from step 3&gt;/attendees after the site address in the browser address bar and press Enter</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="31" customHeight="1">
-      <c r="A6" s="12" t="inlineStr">
-        <is>
-          <t>Test Data</t>
-        </is>
-      </c>
-      <c r="B6" s="13" t="inlineStr">
-        <is>
-          <t>Event: SPM65 Harbourfront Seminar | Operations Manager: Grace Lim | Safety Officer: Hana Yusof</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="98.5" customHeight="1">
-      <c r="A7" s="12" t="inlineStr">
-        <is>
-          <t>Expected Result</t>
-        </is>
-      </c>
-      <c r="B7" s="13" t="inlineStr">
-        <is>
-          <t>Step 2: The event page opens. There is no 'Attendees' tab.
-Step 4: A red message 'Not authorised' says 'You can only view the registrations for events you are responsible for.'
-Step 7: The event page opens with the tabs 'Overview' and 'Equipment'. There is no 'Attendees' tab.
-Step 8: A red message 'Not authorised' says 'You can only view the registrations for events you are responsible for.'</t>
         </is>
       </c>
     </row>
@@ -2966,7 +1919,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="44.5" customHeight="1">
+    <row r="3" ht="58" customHeight="1">
       <c r="A3" s="12" t="inlineStr">
         <is>
           <t>Summary</t>
@@ -2974,7 +1927,7 @@
       </c>
       <c r="B3" s="13" t="inlineStr">
         <is>
-          <t>The organiser responsible for the event opens its Attendees tab and sees each attendee's name, email and registration date</t>
+          <t>The organiser responsible for a full event sees every attendee with their contact details, status and registration date, who was added on their behalf, and the places taken against the waiting list</t>
         </is>
       </c>
     </row>
@@ -2986,7 +1939,7 @@
       </c>
       <c r="B4" s="13" t="inlineStr">
         <is>
-          <t>Test data loaded: `npm run fixtures:spm65` has been run from the project folder since the last full `npx prisma db seed` (it only touches the 'SPM65 …' events, never anyone else's data), and SPM-65-TC08 has not been run since.
+          <t>Test data loaded: `npm run fixtures:spm65` has been run from the project folder since the last full `npx prisma db seed` (it only touches the 'SPM65 …' events, never anyone else's data).
 Logged in as Evelyn Chen (evelyn.chen@straitsmedic.com / password123), who organised every 'SPM65 …' event.
 Nothing is saved in this case.</t>
         </is>
@@ -3014,11 +1967,11 @@
       </c>
       <c r="B6" s="13" t="inlineStr">
         <is>
-          <t>Event: SPM65 Harbourfront Seminar (capacity 3) | Organiser: Evelyn Chen | Attendees: Marcus Yeo, Farhan Ismail, Anita Devi, Tom Harris, Siti Nurhaliza</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="179.5" customHeight="1">
+          <t>Event: SPM65 Harbourfront Seminar (capacity 3) | Registered: Marcus Yeo, Anita Devi (added by Evelyn Chen), Tom Harris | Waiting list: Siti Nurhaliza | Withdrawn: Farhan Ismail</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="247" customHeight="1">
       <c r="A7" s="12" t="inlineStr">
         <is>
           <t>Expected Result</t>
@@ -3027,7 +1980,7 @@
       <c r="B7" s="13" t="inlineStr">
         <is>
           <t>Step 2: The event page opens with the heading 'SPM65 Harbourfront Seminar' and the tabs 'Overview', 'Equipment' and 'Attendees'.
-Step 3: The Attendees page opens with the heading 'SPM65 Harbourfront Seminar', the line 'Who has registered for this event.' and the 'Attendees' tab selected. A table has the columns 'Attendee', 'Contact', 'Status' and 'Registered', and five rows, oldest first: Marcus Yeo, marcus.yeo@example.com, 1 Oct 2026, 10:00; Farhan Ismail, farhan.ismail@example.com, 1 Oct 2026, 16:00; Anita Devi, anita.devi@example.com, 2 Oct 2026, 14:30; Tom Harris, tom.harris@example.com, 3 Oct 2026, 09:15; Siti Nurhaliza, siti.nurhaliza@example.com, 5 Oct 2026, 11:00.</t>
+Step 3: The Attendees page opens with the 'Attendees' tab selected. Above the table it says '3 of 3 places taken · 1 on the waiting list' (the withdrawn and waiting-list attendees are not counted as places taken). The table has the columns 'Attendee', 'Contact', 'Status' and 'Registered', and five rows, oldest first: Marcus Yeo, marcus.yeo@example.com, green 'Registered', 1 Oct 2026, 10:00; Farhan Ismail, farhan.ismail@example.com, grey 'Withdrawn', 1 Oct 2026, 16:00 with 'Withdrew 6 Oct 2026, 12:00' under it; Anita Devi with 'Added by Evelyn Chen' under her name, anita.devi@example.com, green 'Registered', 2 Oct 2026, 14:30; Tom Harris, tom.harris@example.com, green 'Registered', 3 Oct 2026, 09:15; Siti Nurhaliza, siti.nurhaliza@example.com, amber 'Waiting list', 5 Oct 2026, 11:00. No row except Anita Devi's has an 'Added by' line.</t>
         </is>
       </c>
     </row>
@@ -3148,7 +2101,7 @@
       </c>
       <c r="B3" s="13" t="inlineStr">
         <is>
-          <t>Registered, waitlisted and withdrawn attendees each have their own status badge, and a withdrawn one shows when they withdrew</t>
+          <t>Checked-in attendees of a past event are shown as Attended, apart from those who registered but did not come and those who withdrew</t>
         </is>
       </c>
     </row>
@@ -3175,7 +2128,7 @@
       <c r="B5" s="13" t="inlineStr">
         <is>
           <t>1. Click 'My Events' in the sidebar
-2. Click 'SPM65 Harbourfront Seminar' in the list
+2. Click 'SPM65 Past Health Talk' in the list
 3. Click the 'Attendees' tab</t>
         </is>
       </c>
@@ -3188,11 +2141,11 @@
       </c>
       <c r="B6" s="13" t="inlineStr">
         <is>
-          <t>Event: SPM65 Harbourfront Seminar | Registered: Marcus Yeo, Anita Devi, Tom Harris | Waiting list: Siti Nurhaliza | Withdrawn: Farhan Ismail</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="85" customHeight="1">
+          <t>Event: SPM65 Past Health Talk (Completed, 20 Sep 2026, capacity 10) | Attended: Lee Wei Ming, Chua Mei Ling | Registered, did not attend: Jocelyn Pang | Withdrawn: Ravi Subramaniam</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="112" customHeight="1">
       <c r="A7" s="12" t="inlineStr">
         <is>
           <t>Expected Result</t>
@@ -3200,7 +2153,7 @@
       </c>
       <c r="B7" s="13" t="inlineStr">
         <is>
-          <t>Step 3: In the 'Status' column, Marcus Yeo, Anita Devi and Tom Harris have the green badge 'Registered', Siti Nurhaliza has the amber badge 'Waiting list', and Farhan Ismail has the grey badge 'Withdrawn'. Under Farhan Ismail's registration date it says 'Withdrew 6 Oct 2026, 12:00'. No other row has a 'Withdrew' line.</t>
+          <t>Step 3: Above the table it says '3 of 10 places taken · 0 on the waiting list'. Lee Wei Ming (registered 3 Aug 2026, 10:00) and Chua Mei Ling (4 Aug 2026, 10:00) have the blue badge 'Attended'. Jocelyn Pang (5 Aug 2026, 10:00) has the green badge 'Registered'. Ravi Subramaniam (6 Aug 2026, 10:00) has the grey badge 'Withdrawn' and the line 'Withdrew 1 Sept 2026, 10:00'. 'Attended' and 'Registered' are different colours.</t>
         </is>
       </c>
     </row>
@@ -3321,11 +2274,11 @@
       </c>
       <c r="B3" s="13" t="inlineStr">
         <is>
-          <t>An attendee added on the organiser's behalf is marked with who added them, and self-registered attendees are not</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="98.5" customHeight="1">
+          <t>An event with no capacity limit shows how many are registered and says there is no limit</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="71.5" customHeight="1">
       <c r="A4" s="12" t="inlineStr">
         <is>
           <t>Pre-conditions</t>
@@ -3333,7 +2286,7 @@
       </c>
       <c r="B4" s="13" t="inlineStr">
         <is>
-          <t>Test data loaded: `npm run fixtures:spm65` has been run since the last full `npx prisma db seed` (it records Anita Devi's registration for 'SPM65 Harbourfront Seminar' as added by Evelyn Chen).
+          <t>Test data loaded: `npm run fixtures:spm65` has been run since the last full `npx prisma db seed`.
 Logged in as Evelyn Chen (evelyn.chen@straitsmedic.com / password123).
 Nothing is saved in this case.</t>
         </is>
@@ -3348,12 +2301,12 @@
       <c r="B5" s="13" t="inlineStr">
         <is>
           <t>1. Click 'My Events' in the sidebar
-2. Click 'SPM65 Harbourfront Seminar' in the list
+2. Click 'SPM65 Open Lecture' in the list
 3. Click the 'Attendees' tab</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="44.5" customHeight="1">
+    <row r="6" ht="31" customHeight="1">
       <c r="A6" s="12" t="inlineStr">
         <is>
           <t>Test Data</t>
@@ -3361,11 +2314,11 @@
       </c>
       <c r="B6" s="13" t="inlineStr">
         <is>
-          <t>Event: SPM65 Harbourfront Seminar | Added by the organiser: Anita Devi (added by Evelyn Chen) | Self-registered: Marcus Yeo, Farhan Ismail, Tom Harris, Siti Nurhaliza</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="44.5" customHeight="1">
+          <t>Event: SPM65 Open Lecture (registration enabled, no capacity set) | Registered: Anita Devi, Tom Harris</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
       <c r="A7" s="12" t="inlineStr">
         <is>
           <t>Expected Result</t>
@@ -3373,7 +2326,7 @@
       </c>
       <c r="B7" s="13" t="inlineStr">
         <is>
-          <t>Step 3: In the 'Attendee' column, under the name Anita Devi it says 'Added by Evelyn Chen'. Marcus Yeo, Farhan Ismail, Tom Harris and Siti Nurhaliza have no 'Added by' line.</t>
+          <t>Step 3: Above the table it says '2 registered (no capacity limit) · 0 on the waiting list'. The table lists Anita Devi (4 Oct 2026, 10:00) and Tom Harris (4 Oct 2026, 11:00), both with the badge 'Registered'.</t>
         </is>
       </c>
     </row>
@@ -3486,7 +2439,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="44.5" customHeight="1">
+    <row r="3" ht="31" customHeight="1">
       <c r="A3" s="12" t="inlineStr">
         <is>
           <t>Summary</t>
@@ -3494,11 +2447,11 @@
       </c>
       <c r="B3" s="13" t="inlineStr">
         <is>
-          <t>A full event's list shows every place taken against the capacity and the number on the waiting list, not counting withdrawals</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="71.5" customHeight="1">
+          <t>The open list shows a new registration and then its withdrawal within 15 seconds, without refreshing the page</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="85" customHeight="1">
       <c r="A4" s="12" t="inlineStr">
         <is>
           <t>Pre-conditions</t>
@@ -3506,13 +2459,13 @@
       </c>
       <c r="B4" s="13" t="inlineStr">
         <is>
-          <t>Test data loaded: `npm run fixtures:spm65` has been run since the last full `npx prisma db seed`.
-Logged in as Evelyn Chen (evelyn.chen@straitsmedic.com / password123).
-Nothing is saved in this case.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="44.5" customHeight="1">
+          <t>Before and after: run `npm run fixtures:spm65` (never `npx prisma db seed`, which wipes everyone's data).
+Two browser windows: a normal one, and a private (incognito) one, so the two logins don't replace each other.
+In the normal window, logged in as Evelyn Chen (evelyn.chen@straitsmedic.com / password123).</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="233.5" customHeight="1">
       <c r="A5" s="12" t="inlineStr">
         <is>
           <t>Test Steps</t>
@@ -3520,9 +2473,17 @@
       </c>
       <c r="B5" s="13" t="inlineStr">
         <is>
-          <t>1. Click 'My Events' in the sidebar
-2. Click 'SPM65 Harbourfront Seminar' in the list
-3. Click the 'Attendees' tab</t>
+          <t>1. In the normal window, click 'My Events' in the sidebar
+2. Click 'SPM65 Live Update Workshop' in the list
+3. Click the 'Attendees' tab, and leave this window open on it without refreshing
+4. In the private window, go to the site (e.g. http://localhost:3000) and log in as Marcus Yeo (marcus.yeo@example.com / password123), an Attendee
+5. Click 'Browse Events' in the sidebar
+6. Click 'SPM65 Live Update Workshop'
+7. Click 'Register' in the 'Your registration' card
+8. Switch to the normal window and wait up to 15 seconds, without refreshing
+9. Switch to the private window and click 'Withdraw' in the 'Your registration' card
+10. Click 'Withdraw' in the dialog
+11. Switch to the normal window and wait up to 15 seconds, without refreshing</t>
         </is>
       </c>
     </row>
@@ -3534,11 +2495,11 @@
       </c>
       <c r="B6" s="13" t="inlineStr">
         <is>
-          <t>Event: SPM65 Harbourfront Seminar (capacity 3; 3 registered, 1 on the waiting list, 1 withdrawn)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="44.5" customHeight="1">
+          <t>Event: SPM65 Live Update Workshop (capacity 5, nobody registered) | Organiser: Evelyn Chen | Attendee: Marcus Yeo</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="179.5" customHeight="1">
       <c r="A7" s="12" t="inlineStr">
         <is>
           <t>Expected Result</t>
@@ -3546,7 +2507,11 @@
       </c>
       <c r="B7" s="13" t="inlineStr">
         <is>
-          <t>Step 3: Above the table it says '3 of 3 places taken · 1 on the waiting list'. Farhan Ismail (Withdrawn) and Siti Nurhaliza (Waiting list) are not counted in the places taken.</t>
+          <t>Step 3: The Attendees page says '0 of 5 places taken · 0 on the waiting list' and 'No one has registered yet'.
+Step 7: A green message says 'You're registered for this event.'
+Step 8: Without a refresh, the list now has one row, Marcus Yeo, marcus.yeo@example.com, with the badge 'Registered' and today's date and time, and it says '1 of 5 places taken · 0 on the waiting list'.
+Step 10: The dialog closes and a green message says 'You have withdrawn from this event.'
+Step 11: Without a refresh, Marcus Yeo's badge is now 'Withdrawn' with a 'Withdrew' line giving today's date and time, and it says '0 of 5 places taken · 0 on the waiting list'.</t>
         </is>
       </c>
     </row>
@@ -3659,7 +2624,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="44.5" customHeight="1">
+    <row r="3" ht="31" customHeight="1">
       <c r="A3" s="12" t="inlineStr">
         <is>
           <t>Summary</t>
@@ -3667,7 +2632,7 @@
       </c>
       <c r="B3" s="13" t="inlineStr">
         <is>
-          <t>Checked-in attendees of a past event are shown as Attended, apart from those who registered but did not come and those who withdrew</t>
+          <t>When registration is not enabled, the list says so instead of showing an empty list</t>
         </is>
       </c>
     </row>
@@ -3694,12 +2659,12 @@
       <c r="B5" s="13" t="inlineStr">
         <is>
           <t>1. Click 'My Events' in the sidebar
-2. Click 'SPM65 Past Health Talk' in the list
+2. Click 'SPM65 Closed Doors Gala' in the list
 3. Click the 'Attendees' tab</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="44.5" customHeight="1">
+    <row r="6" ht="31" customHeight="1">
       <c r="A6" s="12" t="inlineStr">
         <is>
           <t>Test Data</t>
@@ -3707,11 +2672,11 @@
       </c>
       <c r="B6" s="13" t="inlineStr">
         <is>
-          <t>Event: SPM65 Past Health Talk (Completed, 20 Sep 2026, capacity 10) | Attended: Lee Wei Ming, Chua Mei Ling | Registered, did not attend: Jocelyn Pang | Withdrawn: Ravi Subramaniam</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="112" customHeight="1">
+          <t>Event: SPM65 Closed Doors Gala (registration not enabled, no registrations)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
       <c r="A7" s="12" t="inlineStr">
         <is>
           <t>Expected Result</t>
@@ -3719,7 +2684,7 @@
       </c>
       <c r="B7" s="13" t="inlineStr">
         <is>
-          <t>Step 3: Above the table it says '3 of 10 places taken · 0 on the waiting list'. Lee Wei Ming (registered 3 Aug 2026, 10:00) and Chua Mei Ling (4 Aug 2026, 10:00) have the blue badge 'Attended'. Jocelyn Pang (5 Aug 2026, 10:00) has the green badge 'Registered'. Ravi Subramaniam (6 Aug 2026, 10:00) has the grey badge 'Withdrawn' and the line 'Withdrew 1 Sept 2026, 10:00'. 'Attended' and 'Registered' are different colours.</t>
+          <t>Step 3: A blue message says 'Registration is not enabled for this event' and 'Attendees can't register until the coordinator turns registration on.' There is no table, no 'No one has registered yet' message, and no '… places taken' line.</t>
         </is>
       </c>
     </row>
@@ -3840,7 +2805,7 @@
       </c>
       <c r="B3" s="13" t="inlineStr">
         <is>
-          <t>An event with no capacity limit shows how many are registered and says there is no limit</t>
+          <t>When registration was turned off after someone registered, the list says it is not enabled and still lists that attendee</t>
         </is>
       </c>
     </row>
@@ -3867,7 +2832,7 @@
       <c r="B5" s="13" t="inlineStr">
         <is>
           <t>1. Click 'My Events' in the sidebar
-2. Click 'SPM65 Open Lecture' in the list
+2. Click 'SPM65 Paused Forum' in the list
 3. Click the 'Attendees' tab</t>
         </is>
       </c>
@@ -3880,7 +2845,7 @@
       </c>
       <c r="B6" s="13" t="inlineStr">
         <is>
-          <t>Event: SPM65 Open Lecture (registration enabled, no capacity set) | Registered: Anita Devi, Tom Harris</t>
+          <t>Event: SPM65 Paused Forum (registration turned off, capacity 20) | Registered: Marcus Yeo</t>
         </is>
       </c>
     </row>
@@ -3892,7 +2857,7 @@
       </c>
       <c r="B7" s="13" t="inlineStr">
         <is>
-          <t>Step 3: Above the table it says '2 registered (no capacity limit) · 0 on the waiting list'. The table lists Anita Devi (4 Oct 2026, 10:00) and Tom Harris (4 Oct 2026, 11:00), both with the badge 'Registered'.</t>
+          <t>Step 3: A blue message says 'Registration is not enabled for this event'. Under it, it says '1 of 20 places taken · 0 on the waiting list', and the table lists Marcus Yeo, marcus.yeo@example.com, 'Registered', 2 Oct 2026, 10:00.</t>
         </is>
       </c>
     </row>
@@ -4013,11 +2978,11 @@
       </c>
       <c r="B3" s="13" t="inlineStr">
         <is>
-          <t>An event with registration open and nobody registered says no one has registered yet, with no places taken</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="85" customHeight="1">
+          <t>The coordinator assigned to the event opens its Attendees tab and sees its registrations and places taken</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="71.5" customHeight="1">
       <c r="A4" s="12" t="inlineStr">
         <is>
           <t>Pre-conditions</t>
@@ -4025,8 +2990,8 @@
       </c>
       <c r="B4" s="13" t="inlineStr">
         <is>
-          <t>Test data loaded: `npm run fixtures:spm65` has been run since the last full `npx prisma db seed`, and SPM-65-TC08 has not been run since (it registers attendees for this event).
-Logged in as Evelyn Chen (evelyn.chen@straitsmedic.com / password123).
+          <t>Test data loaded: `npm run fixtures:spm65` has been run since the last full `npx prisma db seed`.
+Logged in as Daniel Tan (daniel.tan@connectsphere.com / password123), the coordinator assigned to every 'SPM65 …' event.
 Nothing is saved in this case.</t>
         </is>
       </c>
@@ -4039,13 +3004,13 @@
       </c>
       <c r="B5" s="13" t="inlineStr">
         <is>
-          <t>1. Click 'My Events' in the sidebar
-2. Click 'SPM65 Live Update Workshop' in the list
+          <t>1. Click 'All Events' in the sidebar
+2. Click 'SPM65 Harbourfront Seminar' in the list
 3. Click the 'Attendees' tab</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="31" customHeight="1">
+    <row r="6" ht="17.5" customHeight="1">
       <c r="A6" s="12" t="inlineStr">
         <is>
           <t>Test Data</t>
@@ -4053,11 +3018,11 @@
       </c>
       <c r="B6" s="13" t="inlineStr">
         <is>
-          <t>Event: SPM65 Live Update Workshop (registration enabled, capacity 5, no registrations)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="58" customHeight="1">
+          <t>Event: SPM65 Harbourfront Seminar | Coordinator: Daniel Tan</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="112" customHeight="1">
       <c r="A7" s="12" t="inlineStr">
         <is>
           <t>Expected Result</t>
@@ -4065,7 +3030,8 @@
       </c>
       <c r="B7" s="13" t="inlineStr">
         <is>
-          <t>Step 3: It says '0 of 5 places taken · 0 on the waiting list', then 'No one has registered yet' and 'Registrations appear here as they come in.' There is no table and no message about registration not being enabled.</t>
+          <t>Step 2: The event page shows the tabs 'Overview', 'Venue', 'Equipment', 'Attendees' and 'Readiness'.
+Step 3: The Attendees page says '3 of 3 places taken · 1 on the waiting list' and lists five rows, oldest first: Marcus Yeo ('Registered'), Farhan Ismail ('Withdrawn'), Anita Devi ('Registered', with 'Added by Evelyn Chen'), Tom Harris ('Registered') and Siti Nurhaliza ('Waiting list'), each with their email address.</t>
         </is>
       </c>
     </row>
@@ -4186,7 +3152,7 @@
       </c>
       <c r="B3" s="13" t="inlineStr">
         <is>
-          <t>The open list shows a new registration and then its withdrawal within 15 seconds, without refreshing the page</t>
+          <t>An organiser at the same client who did not raise the event can open the event but not its registration list</t>
         </is>
       </c>
     </row>
@@ -4198,13 +3164,13 @@
       </c>
       <c r="B4" s="13" t="inlineStr">
         <is>
-          <t>Before and after: run `npm run fixtures:spm65` (never `npx prisma db seed`, which wipes everyone's data).
-Two browser windows: a normal one, and a private (incognito) one, so the two logins don't replace each other.
-In the normal window, logged in as Evelyn Chen (evelyn.chen@straitsmedic.com / password123).</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="233.5" customHeight="1">
+          <t>Test data loaded: `npm run fixtures:spm65` has been run since the last full `npx prisma db seed`.
+Logged in as Raj Kumar (raj.kumar@straitsmedic.com / password123), an Event Organiser at Straits Medical Institute, the same client as Evelyn Chen, who organised the event.
+Nothing is saved in this case.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="44.5" customHeight="1">
       <c r="A5" s="12" t="inlineStr">
         <is>
           <t>Test Steps</t>
@@ -4212,17 +3178,9 @@
       </c>
       <c r="B5" s="13" t="inlineStr">
         <is>
-          <t>1. In the normal window, click 'My Events' in the sidebar
-2. Click 'SPM65 Live Update Workshop' in the list
-3. Click the 'Attendees' tab, and leave this window open on it without refreshing
-4. In the private window, go to the site (e.g. http://localhost:3000) and log in as Marcus Yeo (marcus.yeo@example.com / password123), an Attendee
-5. Click 'Browse Events' in the sidebar
-6. Click 'SPM65 Live Update Workshop'
-7. Click 'Register' in the 'Your registration' card
-8. Switch to the normal window and wait up to 15 seconds, without refreshing
-9. Switch to the private window and click 'Withdraw' in the 'Your registration' card
-10. Click 'Withdraw' in the dialog
-11. Switch to the normal window and wait up to 15 seconds, without refreshing</t>
+          <t>1. Click 'My Events' in the sidebar
+2. Click 'SPM65 Harbourfront Seminar' in the list
+3. Click the 'Attendees' tab</t>
         </is>
       </c>
     </row>
@@ -4234,11 +3192,11 @@
       </c>
       <c r="B6" s="13" t="inlineStr">
         <is>
-          <t>Event: SPM65 Live Update Workshop (capacity 5, nobody registered) | Organiser: Evelyn Chen | Attendee: Marcus Yeo</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="179.5" customHeight="1">
+          <t>Event: SPM65 Harbourfront Seminar (organised by Evelyn Chen) | Organiser: Raj Kumar (same client, not responsible)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="71.5" customHeight="1">
       <c r="A7" s="12" t="inlineStr">
         <is>
           <t>Expected Result</t>
@@ -4246,11 +3204,8 @@
       </c>
       <c r="B7" s="13" t="inlineStr">
         <is>
-          <t>Step 3: The Attendees page says '0 of 5 places taken · 0 on the waiting list' and 'No one has registered yet'.
-Step 7: A green message says 'You're registered for this event.'
-Step 8: Without a refresh, the list now has one row, Marcus Yeo, marcus.yeo@example.com, with the badge 'Registered' and today's date and time, and it says '1 of 5 places taken · 0 on the waiting list'.
-Step 10: The dialog closes and a green message says 'You have withdrawn from this event.'
-Step 11: Without a refresh, Marcus Yeo's badge is now 'Withdrawn' with a 'Withdrew' line giving today's date and time, and it says '0 of 5 places taken · 0 on the waiting list'.</t>
+          <t>Step 2: The event page 'SPM65 Harbourfront Seminar' opens, with an 'Attendees' tab.
+Step 3: A red message 'Not authorised' says 'You can only view the registrations for events you are responsible for.' No attendee names, emails or places taken are shown.</t>
         </is>
       </c>
     </row>
